--- a/panchang-data/Wilton_Connecticut2026.xlsx
+++ b/panchang-data/Wilton_Connecticut2026.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5421">
   <si>
     <t>दिनाङ्क</t>
   </si>
@@ -16288,6 +16288,9 @@
   </si>
   <si>
     <t>121°03'37.38</t>
+  </si>
+  <si>
+    <t>ज्येष्ठ अधिक</t>
   </si>
 </sst>
 </file>
@@ -16777,7 +16780,7 @@
         <v>46023</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>29</v>
@@ -16863,7 +16866,7 @@
         <v>46024</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>50</v>
@@ -16949,7 +16952,7 @@
         <v>46025</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>71</v>
+        <v>568</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>72</v>
@@ -17035,7 +17038,7 @@
         <v>46026</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>71</v>
+        <v>568</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>92</v>
@@ -17121,7 +17124,7 @@
         <v>46027</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>71</v>
+        <v>568</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>109</v>
@@ -17207,7 +17210,7 @@
         <v>46028</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>71</v>
+        <v>568</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>126</v>
@@ -17293,7 +17296,7 @@
         <v>46029</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>71</v>
+        <v>568</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>144</v>
@@ -17379,7 +17382,7 @@
         <v>46030</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>71</v>
+        <v>568</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>29</v>
@@ -17465,7 +17468,7 @@
         <v>46031</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>71</v>
+        <v>568</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>50</v>
@@ -17551,7 +17554,7 @@
         <v>46032</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>71</v>
+        <v>568</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>72</v>
@@ -17637,7 +17640,7 @@
         <v>46033</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>71</v>
+        <v>568</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>92</v>
@@ -17723,7 +17726,7 @@
         <v>46034</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>71</v>
+        <v>568</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>109</v>
@@ -17809,7 +17812,7 @@
         <v>46035</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>71</v>
+        <v>568</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>126</v>
@@ -17895,7 +17898,7 @@
         <v>46036</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>71</v>
+        <v>568</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>144</v>
@@ -17981,7 +17984,7 @@
         <v>46037</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>71</v>
+        <v>568</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>29</v>
@@ -18067,7 +18070,7 @@
         <v>46038</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>71</v>
+        <v>568</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>50</v>
@@ -18153,7 +18156,7 @@
         <v>46039</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>71</v>
+        <v>568</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>72</v>
@@ -18239,7 +18242,7 @@
         <v>46040</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>71</v>
+        <v>568</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>92</v>
@@ -18325,7 +18328,7 @@
         <v>46041</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>71</v>
+        <v>568</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>109</v>
@@ -18411,7 +18414,7 @@
         <v>46042</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>71</v>
+        <v>568</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>126</v>
@@ -18497,7 +18500,7 @@
         <v>46043</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>71</v>
+        <v>568</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>144</v>
@@ -18583,7 +18586,7 @@
         <v>46044</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>71</v>
+        <v>568</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>29</v>
@@ -18669,7 +18672,7 @@
         <v>46045</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>71</v>
+        <v>568</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>50</v>
@@ -18755,7 +18758,7 @@
         <v>46046</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>71</v>
+        <v>568</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>72</v>
@@ -18841,7 +18844,7 @@
         <v>46047</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>71</v>
+        <v>568</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>92</v>
@@ -18927,7 +18930,7 @@
         <v>46048</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>71</v>
+        <v>568</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>109</v>
@@ -19013,7 +19016,7 @@
         <v>46049</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>71</v>
+        <v>568</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>126</v>
@@ -19099,7 +19102,7 @@
         <v>46050</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>71</v>
+        <v>568</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>144</v>
@@ -19185,7 +19188,7 @@
         <v>46051</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>71</v>
+        <v>568</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>29</v>
@@ -19271,7 +19274,7 @@
         <v>46052</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>71</v>
+        <v>568</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>50</v>
@@ -19357,7 +19360,7 @@
         <v>46053</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>71</v>
+        <v>568</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>72</v>
@@ -19443,7 +19446,7 @@
         <v>46054</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>71</v>
+        <v>568</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>92</v>
@@ -19529,7 +19532,7 @@
         <v>46055</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>568</v>
+        <v>997</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>109</v>
@@ -19615,7 +19618,7 @@
         <v>46056</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>568</v>
+        <v>997</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>126</v>
@@ -19701,7 +19704,7 @@
         <v>46057</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>568</v>
+        <v>997</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>144</v>
@@ -19787,7 +19790,7 @@
         <v>46058</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>568</v>
+        <v>997</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>29</v>
@@ -19873,7 +19876,7 @@
         <v>46059</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>568</v>
+        <v>997</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>50</v>
@@ -19959,7 +19962,7 @@
         <v>46060</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>568</v>
+        <v>997</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>72</v>
@@ -20045,7 +20048,7 @@
         <v>46061</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>568</v>
+        <v>997</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>92</v>
@@ -20131,7 +20134,7 @@
         <v>46062</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>568</v>
+        <v>997</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>109</v>
@@ -20217,7 +20220,7 @@
         <v>46063</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>568</v>
+        <v>997</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>126</v>
@@ -20303,7 +20306,7 @@
         <v>46064</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>568</v>
+        <v>997</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>144</v>
@@ -20389,7 +20392,7 @@
         <v>46065</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>568</v>
+        <v>997</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>29</v>
@@ -20475,7 +20478,7 @@
         <v>46066</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>568</v>
+        <v>997</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>50</v>
@@ -20561,7 +20564,7 @@
         <v>46067</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>568</v>
+        <v>997</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>72</v>
@@ -20647,7 +20650,7 @@
         <v>46068</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>568</v>
+        <v>997</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>92</v>
@@ -20733,7 +20736,7 @@
         <v>46069</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>568</v>
+        <v>997</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>109</v>
@@ -20819,7 +20822,7 @@
         <v>46070</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>568</v>
+        <v>997</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>126</v>
@@ -20905,7 +20908,7 @@
         <v>46071</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>568</v>
+        <v>997</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>144</v>
@@ -20991,7 +20994,7 @@
         <v>46072</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>568</v>
+        <v>997</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>29</v>
@@ -21077,7 +21080,7 @@
         <v>46073</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>568</v>
+        <v>997</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>50</v>
@@ -21163,7 +21166,7 @@
         <v>46074</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>568</v>
+        <v>997</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>72</v>
@@ -21249,7 +21252,7 @@
         <v>46075</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>568</v>
+        <v>997</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>92</v>
@@ -21335,7 +21338,7 @@
         <v>46076</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>568</v>
+        <v>997</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>109</v>
@@ -21421,7 +21424,7 @@
         <v>46077</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>568</v>
+        <v>997</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>126</v>
@@ -21507,7 +21510,7 @@
         <v>46078</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>568</v>
+        <v>997</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>144</v>
@@ -21593,7 +21596,7 @@
         <v>46079</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>568</v>
+        <v>997</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>29</v>
@@ -21679,7 +21682,7 @@
         <v>46080</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>568</v>
+        <v>997</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>50</v>
@@ -21765,7 +21768,7 @@
         <v>46081</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>568</v>
+        <v>997</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>72</v>
@@ -21851,7 +21854,7 @@
         <v>46082</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>568</v>
+        <v>997</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>92</v>
@@ -21937,7 +21940,7 @@
         <v>46083</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>568</v>
+        <v>997</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>109</v>
@@ -22023,7 +22026,7 @@
         <v>46084</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>997</v>
+        <v>1438</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>126</v>
@@ -22109,7 +22112,7 @@
         <v>46085</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>997</v>
+        <v>1438</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>144</v>
@@ -22195,7 +22198,7 @@
         <v>46086</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>997</v>
+        <v>1438</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>29</v>
@@ -22281,7 +22284,7 @@
         <v>46087</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>997</v>
+        <v>1438</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>50</v>
@@ -22367,7 +22370,7 @@
         <v>46088</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>997</v>
+        <v>1438</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>72</v>
@@ -22453,7 +22456,7 @@
         <v>46089</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>997</v>
+        <v>1438</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>92</v>
@@ -22539,7 +22542,7 @@
         <v>46090</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>997</v>
+        <v>1438</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>109</v>
@@ -22625,7 +22628,7 @@
         <v>46091</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>997</v>
+        <v>1438</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>126</v>
@@ -22711,7 +22714,7 @@
         <v>46092</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>997</v>
+        <v>1438</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>144</v>
@@ -22797,7 +22800,7 @@
         <v>46093</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>997</v>
+        <v>1438</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>29</v>
@@ -22883,7 +22886,7 @@
         <v>46094</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>997</v>
+        <v>1438</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>50</v>
@@ -22969,7 +22972,7 @@
         <v>46095</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>997</v>
+        <v>1438</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>72</v>
@@ -23055,7 +23058,7 @@
         <v>46096</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>997</v>
+        <v>1438</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>92</v>
@@ -23141,7 +23144,7 @@
         <v>46097</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>997</v>
+        <v>1438</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>109</v>
@@ -23227,7 +23230,7 @@
         <v>46098</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>997</v>
+        <v>1438</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>126</v>
@@ -23313,7 +23316,7 @@
         <v>46099</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>997</v>
+        <v>1438</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>144</v>
@@ -23399,7 +23402,7 @@
         <v>46100</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>997</v>
+        <v>1438</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>29</v>
@@ -23485,7 +23488,7 @@
         <v>46101</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>997</v>
+        <v>1438</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>50</v>
@@ -23571,7 +23574,7 @@
         <v>46102</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>997</v>
+        <v>1438</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>72</v>
@@ -23657,7 +23660,7 @@
         <v>46103</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>997</v>
+        <v>1438</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>92</v>
@@ -23743,7 +23746,7 @@
         <v>46104</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>997</v>
+        <v>1438</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>109</v>
@@ -23829,7 +23832,7 @@
         <v>46105</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>997</v>
+        <v>1438</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>126</v>
@@ -23915,7 +23918,7 @@
         <v>46106</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>997</v>
+        <v>1438</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>144</v>
@@ -24001,7 +24004,7 @@
         <v>46107</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>997</v>
+        <v>1438</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>29</v>
@@ -24087,7 +24090,7 @@
         <v>46108</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>997</v>
+        <v>1438</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>50</v>
@@ -24173,7 +24176,7 @@
         <v>46109</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>997</v>
+        <v>1438</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>72</v>
@@ -24259,7 +24262,7 @@
         <v>46110</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>997</v>
+        <v>1438</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>92</v>
@@ -24345,7 +24348,7 @@
         <v>46111</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>997</v>
+        <v>1438</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>109</v>
@@ -24431,7 +24434,7 @@
         <v>46112</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>997</v>
+        <v>1438</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>126</v>
@@ -24517,7 +24520,7 @@
         <v>46113</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>997</v>
+        <v>1438</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>144</v>
@@ -24603,7 +24606,7 @@
         <v>46114</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>1438</v>
+        <v>1876</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>29</v>
@@ -24689,7 +24692,7 @@
         <v>46115</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>1438</v>
+        <v>1876</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>50</v>
@@ -24775,7 +24778,7 @@
         <v>46116</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>1438</v>
+        <v>1876</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>72</v>
@@ -24861,7 +24864,7 @@
         <v>46117</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>1438</v>
+        <v>1876</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>92</v>
@@ -24947,7 +24950,7 @@
         <v>46118</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>1438</v>
+        <v>1876</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>109</v>
@@ -25033,7 +25036,7 @@
         <v>46119</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>1438</v>
+        <v>1876</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>126</v>
@@ -25119,7 +25122,7 @@
         <v>46120</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>1438</v>
+        <v>1876</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>144</v>
@@ -25205,7 +25208,7 @@
         <v>46121</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>1438</v>
+        <v>1876</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>29</v>
@@ -25291,7 +25294,7 @@
         <v>46122</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>1438</v>
+        <v>1876</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>50</v>
@@ -25377,7 +25380,7 @@
         <v>46123</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>1438</v>
+        <v>1876</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>72</v>
@@ -25463,7 +25466,7 @@
         <v>46124</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>1438</v>
+        <v>1876</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>92</v>
@@ -25549,7 +25552,7 @@
         <v>46125</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>1438</v>
+        <v>1876</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>109</v>
@@ -25635,7 +25638,7 @@
         <v>46126</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>1438</v>
+        <v>1876</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>126</v>
@@ -25721,7 +25724,7 @@
         <v>46127</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>1438</v>
+        <v>1876</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>144</v>
@@ -25807,7 +25810,7 @@
         <v>46128</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>1438</v>
+        <v>1876</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>29</v>
@@ -25893,7 +25896,7 @@
         <v>46129</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>1438</v>
+        <v>1876</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>50</v>
@@ -25979,7 +25982,7 @@
         <v>46130</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>1438</v>
+        <v>1876</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>72</v>
@@ -26065,7 +26068,7 @@
         <v>46131</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>1438</v>
+        <v>1876</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>92</v>
@@ -26151,7 +26154,7 @@
         <v>46132</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>1438</v>
+        <v>1876</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>109</v>
@@ -26237,7 +26240,7 @@
         <v>46133</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>1438</v>
+        <v>1876</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>126</v>
@@ -26323,7 +26326,7 @@
         <v>46134</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>1438</v>
+        <v>1876</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>144</v>
@@ -26409,7 +26412,7 @@
         <v>46135</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>1438</v>
+        <v>1876</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>29</v>
@@ -26495,7 +26498,7 @@
         <v>46136</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>1438</v>
+        <v>1876</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>50</v>
@@ -26581,7 +26584,7 @@
         <v>46137</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>1438</v>
+        <v>1876</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>72</v>
@@ -26667,7 +26670,7 @@
         <v>46138</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>1438</v>
+        <v>1876</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>92</v>
@@ -26753,7 +26756,7 @@
         <v>46139</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>1438</v>
+        <v>1876</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>109</v>
@@ -26839,7 +26842,7 @@
         <v>46140</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>1438</v>
+        <v>1876</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>126</v>
@@ -26925,7 +26928,7 @@
         <v>46141</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>1438</v>
+        <v>1876</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>144</v>
@@ -27011,7 +27014,7 @@
         <v>46142</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>1438</v>
+        <v>1876</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>29</v>
@@ -27097,7 +27100,7 @@
         <v>46143</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>1438</v>
+        <v>1876</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>50</v>
@@ -27183,7 +27186,7 @@
         <v>46144</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>1876</v>
+        <v>2297</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>72</v>
@@ -27269,7 +27272,7 @@
         <v>46145</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>1876</v>
+        <v>2297</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>92</v>
@@ -27355,7 +27358,7 @@
         <v>46146</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>1876</v>
+        <v>2297</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>109</v>
@@ -27441,7 +27444,7 @@
         <v>46147</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>1876</v>
+        <v>2297</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>126</v>
@@ -27527,7 +27530,7 @@
         <v>46148</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>1876</v>
+        <v>2297</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>144</v>
@@ -27613,7 +27616,7 @@
         <v>46149</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>1876</v>
+        <v>2297</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>29</v>
@@ -27699,7 +27702,7 @@
         <v>46150</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>1876</v>
+        <v>2297</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>50</v>
@@ -27785,7 +27788,7 @@
         <v>46151</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>1876</v>
+        <v>2297</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>72</v>
@@ -27871,7 +27874,7 @@
         <v>46152</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>1876</v>
+        <v>2297</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>92</v>
@@ -27957,7 +27960,7 @@
         <v>46153</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>1876</v>
+        <v>2297</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>109</v>
@@ -28043,7 +28046,7 @@
         <v>46154</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>1876</v>
+        <v>2297</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>126</v>
@@ -28129,7 +28132,7 @@
         <v>46155</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>1876</v>
+        <v>2297</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>144</v>
@@ -28215,7 +28218,7 @@
         <v>46156</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>1876</v>
+        <v>2297</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>29</v>
@@ -28301,7 +28304,7 @@
         <v>46157</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>1876</v>
+        <v>2297</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>50</v>
@@ -28387,7 +28390,7 @@
         <v>46158</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>1876</v>
+        <v>2297</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>72</v>
@@ -28473,7 +28476,7 @@
         <v>46159</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>1876</v>
+        <v>5420</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>92</v>
@@ -28559,7 +28562,7 @@
         <v>46160</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>1876</v>
+        <v>5420</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>109</v>
@@ -28645,7 +28648,7 @@
         <v>46161</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>1876</v>
+        <v>5420</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>126</v>
@@ -28731,7 +28734,7 @@
         <v>46162</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>1876</v>
+        <v>5420</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>144</v>
@@ -28817,7 +28820,7 @@
         <v>46163</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>1876</v>
+        <v>5420</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>29</v>
@@ -28903,7 +28906,7 @@
         <v>46164</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>1876</v>
+        <v>5420</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>50</v>
@@ -28989,7 +28992,7 @@
         <v>46165</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>1876</v>
+        <v>5420</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>72</v>
@@ -29075,7 +29078,7 @@
         <v>46166</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>1876</v>
+        <v>5420</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>92</v>
@@ -29161,7 +29164,7 @@
         <v>46167</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>1876</v>
+        <v>5420</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>109</v>
@@ -29247,7 +29250,7 @@
         <v>46168</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>1876</v>
+        <v>5420</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>126</v>
@@ -29333,7 +29336,7 @@
         <v>46169</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>1876</v>
+        <v>5420</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>144</v>
@@ -29419,7 +29422,7 @@
         <v>46170</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>1876</v>
+        <v>5420</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>29</v>
@@ -29505,7 +29508,7 @@
         <v>46171</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>1876</v>
+        <v>5420</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>50</v>
@@ -29591,7 +29594,7 @@
         <v>46172</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>1876</v>
+        <v>5420</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>72</v>
@@ -29677,7 +29680,7 @@
         <v>46173</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>2297</v>
+        <v>5420</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>92</v>
@@ -29763,7 +29766,7 @@
         <v>46174</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>2297</v>
+        <v>5420</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>109</v>
@@ -29849,7 +29852,7 @@
         <v>46175</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>2297</v>
+        <v>5420</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>126</v>
@@ -29935,7 +29938,7 @@
         <v>46176</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>2297</v>
+        <v>5420</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>144</v>
@@ -30021,7 +30024,7 @@
         <v>46177</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>2297</v>
+        <v>5420</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>29</v>
@@ -30107,7 +30110,7 @@
         <v>46178</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>2297</v>
+        <v>5420</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>50</v>
@@ -30193,7 +30196,7 @@
         <v>46179</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>2297</v>
+        <v>5420</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>72</v>
@@ -30279,7 +30282,7 @@
         <v>46180</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>2297</v>
+        <v>5420</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>92</v>
@@ -30365,7 +30368,7 @@
         <v>46181</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>2297</v>
+        <v>5420</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>109</v>
@@ -30451,7 +30454,7 @@
         <v>46182</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>2297</v>
+        <v>5420</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>126</v>
@@ -30537,7 +30540,7 @@
         <v>46183</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>2297</v>
+        <v>5420</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>144</v>
@@ -30623,7 +30626,7 @@
         <v>46184</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>2297</v>
+        <v>5420</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>29</v>
@@ -30709,7 +30712,7 @@
         <v>46185</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>2297</v>
+        <v>5420</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>50</v>
@@ -30795,7 +30798,7 @@
         <v>46186</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>2297</v>
+        <v>5420</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>72</v>
@@ -30881,7 +30884,7 @@
         <v>46187</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>2297</v>
+        <v>5420</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>92</v>
